--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N109_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N109_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.82872716539531</v>
+        <v>11.99716816437674</v>
       </c>
       <c r="D2" t="n">
-        <v>37.4297149794799</v>
+        <v>6.082328684165485</v>
       </c>
       <c r="E2" t="n">
-        <v>18.71849180577516</v>
+        <v>3.041754918438464</v>
       </c>
       <c r="F2" t="n">
-        <v>14.77659677491227</v>
+        <v>2.401196975923245</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.23720393240719</v>
+        <v>7.351045639016169</v>
       </c>
       <c r="D3" t="n">
-        <v>44.82449372512548</v>
+        <v>7.28398023033289</v>
       </c>
       <c r="E3" t="n">
-        <v>18.71849180577516</v>
+        <v>3.041754918438464</v>
       </c>
       <c r="F3" t="n">
-        <v>14.77659677491227</v>
+        <v>2.401196975923245</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.77311501054756</v>
+        <v>8.738131189213979</v>
       </c>
       <c r="D4" t="n">
-        <v>27.80753862661603</v>
+        <v>4.518725026825106</v>
       </c>
       <c r="E4" t="n">
-        <v>18.71849180577516</v>
+        <v>3.041754918438464</v>
       </c>
       <c r="F4" t="n">
-        <v>14.77659677491227</v>
+        <v>2.401196975923245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.27054913534223</v>
+        <v>1.993964234493112</v>
       </c>
       <c r="D5" t="n">
-        <v>12.74973945806875</v>
+        <v>2.071832661936172</v>
       </c>
       <c r="E5" t="n">
-        <v>18.71849180577516</v>
+        <v>3.041754918438464</v>
       </c>
       <c r="F5" t="n">
-        <v>14.77659677491227</v>
+        <v>2.401196975923245</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.91358707013933</v>
+        <v>7.948457898897641</v>
       </c>
       <c r="D6" t="n">
-        <v>49.45587290918248</v>
+        <v>8.036579347742153</v>
       </c>
       <c r="E6" t="n">
-        <v>18.71849180577516</v>
+        <v>3.041754918438464</v>
       </c>
       <c r="F6" t="n">
-        <v>14.77659677491227</v>
+        <v>2.401196975923245</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.86365062382405</v>
+        <v>4.852843226371409</v>
       </c>
       <c r="D7" t="n">
-        <v>29.86359291813535</v>
+        <v>4.852833849196994</v>
       </c>
       <c r="E7" t="n">
-        <v>18.71849180577516</v>
+        <v>3.041754918438464</v>
       </c>
       <c r="F7" t="n">
-        <v>14.77659677491227</v>
+        <v>2.401196975923245</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>60.54406695285633</v>
+        <v>9.838410879839154</v>
       </c>
       <c r="D8" t="n">
-        <v>61.31454243979227</v>
+        <v>9.963613146466244</v>
       </c>
       <c r="E8" t="n">
-        <v>18.71849180577516</v>
+        <v>3.041754918438464</v>
       </c>
       <c r="F8" t="n">
-        <v>14.77659677491227</v>
+        <v>2.401196975923245</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
